--- a/Carbon_Emission_Data.xlsx
+++ b/Carbon_Emission_Data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e41f0c43ef017dfa/Documents/Final Year UTP/FYP/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{240EA593-7E56-4943-9F03-314AD552D842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{240EA593-7E56-4943-9F03-314AD552D842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{489C09D5-39A4-446C-96AF-CFB70C668140}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{967E4E1E-6F5B-463E-A9E7-AEF39E419312}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="17">
   <si>
     <t>company</t>
   </si>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,12 +108,6 @@
       <sz val="11"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -129,7 +123,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -152,30 +146,473 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -186,6 +623,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EB600A3C-4F2B-433C-ACF0-748F56EA162C}" name="Table2" displayName="Table2" ref="A1:G56" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:G56" xr:uid="{EB600A3C-4F2B-433C-ACF0-748F56EA162C}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1A5F8F1F-8AB9-4F7C-B221-116272585BE6}" name="company" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{AC925EEE-C329-4B50-995E-7B9CD69B785D}" name="year" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{9BC11FBC-0204-4F90-81F2-69EED4E663E9}" name="scope1_mt_co2e" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{E733596A-276C-4C22-A46E-01A38192C38B}" name="scope2_location_mt_co2e" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{6C8F0934-B69A-4C9B-BFDB-B17DABC69697}" name="scope1_plus_2_mt_co2e" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{8D7E929A-0AD7-43D4-B82C-50458B12FF8B}" name="employees_000s" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{9665514E-96DA-4580-AF74-681994502419}" name="data_notes" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -504,1194 +957,1311 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE247DF-FDAF-4944-987C-1396EC306251}">
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="44.44140625" defaultRowHeight="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08F62E07-CA1F-436B-AE77-202EDCA1A131}">
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr defaultColWidth="34.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="44.44140625" style="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="26.44140625" customWidth="1"/>
+    <col min="5" max="5" width="24.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="34.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="12" customFormat="1" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="1">
         <v>2015</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>119</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>9</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <v>128</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>73.5</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="1">
         <v>2016</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="2">
         <v>112</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>8</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="2">
         <v>120</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="2">
         <v>71.099999999999994</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="1">
         <v>2017</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="2">
         <v>106</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="2">
         <v>114</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="2">
         <v>69.599999999999994</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>2018</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="2">
         <v>100</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>8</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="2">
         <v>108</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="2">
         <v>71</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="1">
         <v>2019</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="2">
         <v>99</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2">
         <v>8</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="2">
         <v>107</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="2">
         <v>74.900000000000006</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="1">
         <v>2020</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="2">
         <v>97</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>8</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="2">
         <v>105</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="2">
         <v>72</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="1">
         <v>2021</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="2">
         <v>98</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2">
         <v>7</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="2">
         <v>105</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="2">
         <v>62</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="1">
         <v>2022</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="2">
         <v>97</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="2">
         <v>7</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="2">
         <v>104</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="2">
         <v>62</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="1">
         <v>2023</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="2">
         <v>93</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="2">
         <v>7</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="2">
         <v>100</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="2">
         <v>62</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="1">
         <v>2024</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="2">
         <v>92</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="2">
         <v>8</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="2">
         <v>100</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="2">
         <v>61</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C12" s="2">
+        <v>92</v>
+      </c>
+      <c r="D12" s="2">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2">
+        <v>100</v>
+      </c>
+      <c r="F12" s="2">
+        <v>58</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B13" s="1">
         <v>2015</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C13" s="2">
         <v>51.2</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D13" s="2">
         <v>6.2</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E13" s="2">
         <v>57.4</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="2">
         <v>74</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4">
-        <v>2016</v>
-      </c>
-      <c r="C13" s="5">
-        <v>51.4</v>
-      </c>
-      <c r="D13" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="E13" s="5">
-        <v>57.6</v>
-      </c>
-      <c r="F13" s="5">
-        <v>75</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="4">
-        <v>2017</v>
-      </c>
-      <c r="C14" s="5">
-        <v>50.5</v>
-      </c>
-      <c r="D14" s="5">
-        <v>6.1</v>
-      </c>
-      <c r="E14" s="5">
-        <v>56.6</v>
-      </c>
-      <c r="F14" s="5">
-        <v>73</v>
+      <c r="B14" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C14" s="2">
+        <v>51.4</v>
+      </c>
+      <c r="D14" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>57.6</v>
+      </c>
+      <c r="F14" s="2">
+        <v>75</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C15" s="5">
-        <v>48.8</v>
-      </c>
-      <c r="D15" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="E15" s="5">
-        <v>54.199999999999903</v>
-      </c>
-      <c r="F15" s="5">
-        <v>72</v>
+      <c r="B15" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C15" s="2">
+        <v>50.5</v>
+      </c>
+      <c r="D15" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>56.6</v>
+      </c>
+      <c r="F15" s="2">
+        <v>73</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="4">
-        <v>2019</v>
-      </c>
-      <c r="C16" s="5">
-        <v>49.2</v>
-      </c>
-      <c r="D16" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="E16" s="5">
-        <v>54.4</v>
-      </c>
-      <c r="F16" s="5">
-        <v>70</v>
+      <c r="B16" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C16" s="2">
+        <v>48.8</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>54.199999999999903</v>
+      </c>
+      <c r="F16" s="2">
+        <v>72</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="4">
-        <v>2020</v>
-      </c>
-      <c r="C17" s="5">
-        <v>41.7</v>
-      </c>
-      <c r="D17" s="5">
-        <v>3.8</v>
-      </c>
-      <c r="E17" s="5">
-        <v>45.5</v>
-      </c>
-      <c r="F17" s="5">
-        <v>66</v>
+      <c r="B17" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C17" s="2">
+        <v>49.2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>54.4</v>
+      </c>
+      <c r="F17" s="2">
+        <v>70</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="4">
-        <v>2021</v>
-      </c>
-      <c r="C18" s="5">
-        <v>33.200000000000003</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.4</v>
-      </c>
-      <c r="E18" s="5">
-        <v>35.6</v>
-      </c>
-      <c r="F18" s="5">
-        <v>67</v>
+      <c r="B18" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C18" s="2">
+        <v>41.7</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="F18" s="2">
+        <v>66</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="4">
-        <v>2022</v>
-      </c>
-      <c r="C19" s="5">
-        <v>30.4</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="E19" s="5">
-        <v>31.799999999999901</v>
-      </c>
-      <c r="F19" s="5">
-        <v>68</v>
+      <c r="B19" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C19" s="2">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>35.6</v>
+      </c>
+      <c r="F19" s="2">
+        <v>67</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="4">
-        <v>2023</v>
-      </c>
-      <c r="C20" s="5">
-        <v>31.1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5">
-        <v>32.1</v>
-      </c>
-      <c r="F20" s="5">
-        <v>88</v>
+      <c r="B20" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C20" s="2">
+        <v>30.4</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>31.799999999999901</v>
+      </c>
+      <c r="F20" s="2">
+        <v>68</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="4">
-        <v>2024</v>
-      </c>
-      <c r="C21" s="5">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="D21" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="E21" s="5">
-        <v>33.599999999999902</v>
-      </c>
-      <c r="F21" s="5">
-        <v>101</v>
+      <c r="B21" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C21" s="2">
+        <v>31.1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2">
+        <v>32.1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>88</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C22" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E22" s="2">
+        <v>33.599999999999902</v>
+      </c>
+      <c r="F22" s="2">
+        <v>101</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C23" s="2">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="F23" s="2">
+        <v>102</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B24" s="1">
         <v>2015</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C24" s="2">
         <v>66</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D24" s="2">
         <v>2</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E24" s="2">
         <v>68</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F24" s="2">
         <v>58.2</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="4">
-        <v>2016</v>
-      </c>
-      <c r="C23" s="5">
-        <v>64</v>
-      </c>
-      <c r="D23" s="5">
-        <v>2</v>
-      </c>
-      <c r="E23" s="5">
-        <v>66</v>
-      </c>
-      <c r="F23" s="5">
-        <v>52</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="4">
-        <v>2017</v>
-      </c>
-      <c r="C24" s="5">
-        <v>64</v>
-      </c>
-      <c r="D24" s="5">
-        <v>2</v>
-      </c>
-      <c r="E24" s="5">
-        <v>66</v>
-      </c>
-      <c r="F24" s="5">
-        <v>48.5</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C25" s="5">
+      <c r="B25" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C25" s="2">
+        <v>64</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2">
         <v>66</v>
       </c>
-      <c r="D25" s="5">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5">
-        <v>68</v>
-      </c>
-      <c r="F25" s="5">
-        <v>45</v>
+      <c r="F25" s="2">
+        <v>52</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="4">
-        <v>2019</v>
-      </c>
-      <c r="C26" s="5">
-        <v>60</v>
-      </c>
-      <c r="D26" s="5">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5">
-        <v>61</v>
-      </c>
-      <c r="F26" s="5">
-        <v>44.7</v>
+      <c r="B26" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C26" s="2">
+        <v>64</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>66</v>
+      </c>
+      <c r="F26" s="2">
+        <v>48.5</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="4">
-        <v>2020</v>
-      </c>
-      <c r="C27" s="5">
-        <v>56</v>
-      </c>
-      <c r="D27" s="5">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5">
-        <v>57</v>
-      </c>
-      <c r="F27" s="5">
-        <v>42.6</v>
+      <c r="B27" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C27" s="2">
+        <v>66</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>68</v>
+      </c>
+      <c r="F27" s="2">
+        <v>45</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="4">
-        <v>2021</v>
-      </c>
-      <c r="C28" s="5">
-        <v>57</v>
-      </c>
-      <c r="D28" s="5">
-        <v>2</v>
-      </c>
-      <c r="E28" s="5">
-        <v>59</v>
-      </c>
-      <c r="F28" s="5">
-        <v>37.5</v>
+      <c r="B28" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C28" s="2">
+        <v>60</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>61</v>
+      </c>
+      <c r="F28" s="2">
+        <v>44.7</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="4">
-        <v>2022</v>
-      </c>
-      <c r="C29" s="5">
-        <v>53</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="B29" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C29" s="2">
+        <v>56</v>
+      </c>
+      <c r="D29" s="2">
         <v>1</v>
       </c>
-      <c r="E29" s="5">
-        <v>54</v>
-      </c>
-      <c r="F29" s="5">
-        <v>38.299999999999997</v>
+      <c r="E29" s="2">
+        <v>57</v>
+      </c>
+      <c r="F29" s="2">
+        <v>42.6</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="4">
-        <v>2023</v>
-      </c>
-      <c r="C30" s="5">
-        <v>52</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="B30" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C30" s="2">
+        <v>57</v>
+      </c>
+      <c r="D30" s="2">
         <v>2</v>
       </c>
-      <c r="E30" s="5">
-        <v>54</v>
-      </c>
-      <c r="F30" s="5">
-        <v>40.200000000000003</v>
+      <c r="E30" s="2">
+        <v>59</v>
+      </c>
+      <c r="F30" s="2">
+        <v>37.5</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="4">
-        <v>2024</v>
-      </c>
-      <c r="C31" s="5">
-        <v>52</v>
-      </c>
-      <c r="D31" s="5">
-        <v>2</v>
-      </c>
-      <c r="E31" s="5">
+      <c r="B31" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C31" s="2">
+        <v>53</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
         <v>54</v>
       </c>
-      <c r="F31" s="5">
-        <v>41</v>
+      <c r="F31" s="2">
+        <v>38.299999999999997</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C32" s="2">
+        <v>52</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>54</v>
+      </c>
+      <c r="F32" s="2">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C33" s="2">
+        <v>52</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>54</v>
+      </c>
+      <c r="F33" s="2">
+        <v>41</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C34" s="2">
+        <v>52</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2">
+        <v>54</v>
+      </c>
+      <c r="F34" s="2">
+        <v>43</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B35" s="1">
         <v>2015</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C35" s="2">
         <v>15.39</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D35" s="2">
         <v>0.2</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E35" s="2">
         <v>15.59</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F35" s="2">
         <v>21.581</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="4">
-        <v>2016</v>
-      </c>
-      <c r="C33" s="5">
-        <v>15.14</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0.19</v>
-      </c>
-      <c r="E33" s="5">
-        <v>15.33</v>
-      </c>
-      <c r="F33" s="5">
-        <v>20.539000000000001</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="4">
-        <v>2017</v>
-      </c>
-      <c r="C34" s="5">
-        <v>14.95</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E34" s="5">
-        <v>15.149999999999901</v>
-      </c>
-      <c r="F34" s="5">
-        <v>20.245000000000001</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C35" s="5">
-        <v>14.72</v>
-      </c>
-      <c r="D35" s="5">
-        <v>0.22</v>
-      </c>
-      <c r="E35" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="F35" s="5">
-        <v>20.524999999999999</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="4">
-        <v>2019</v>
-      </c>
-      <c r="C36" s="5">
-        <v>13.29</v>
-      </c>
-      <c r="D36" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="E36" s="5">
-        <v>13.54</v>
-      </c>
-      <c r="F36" s="5">
-        <v>21.411999999999999</v>
+      <c r="B36" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C36" s="2">
+        <v>15.14</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="E36" s="2">
+        <v>15.33</v>
+      </c>
+      <c r="F36" s="2">
+        <v>20.539000000000001</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B37" s="4">
-        <v>2020</v>
-      </c>
-      <c r="C37" s="5">
-        <v>12.01</v>
-      </c>
-      <c r="D37" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="E37" s="5">
-        <v>12.11</v>
-      </c>
-      <c r="F37" s="5">
-        <v>21.245000000000001</v>
+      <c r="B37" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C37" s="2">
+        <v>14.95</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E37" s="2">
+        <v>15.149999999999901</v>
+      </c>
+      <c r="F37" s="2">
+        <v>20.245000000000001</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="4">
-        <v>2021</v>
-      </c>
-      <c r="C38" s="5">
-        <v>11.37</v>
-      </c>
-      <c r="D38" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E38" s="5">
-        <v>11.44</v>
-      </c>
-      <c r="F38" s="5">
-        <v>21.126000000000001</v>
+      <c r="B38" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C38" s="2">
+        <v>14.72</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.22</v>
+      </c>
+      <c r="E38" s="2">
+        <v>14.94</v>
+      </c>
+      <c r="F38" s="2">
+        <v>20.524999999999999</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B39" s="4">
-        <v>2022</v>
-      </c>
-      <c r="C39" s="5">
-        <v>11.48</v>
-      </c>
-      <c r="D39" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="E39" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="F39" s="5">
-        <v>21.936</v>
+      <c r="B39" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C39" s="2">
+        <v>13.29</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E39" s="2">
+        <v>13.54</v>
+      </c>
+      <c r="F39" s="2">
+        <v>21.411999999999999</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="4">
-        <v>2023</v>
-      </c>
-      <c r="C40" s="5">
-        <v>10.9</v>
-      </c>
-      <c r="D40" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="E40" s="5">
-        <v>11.01</v>
-      </c>
-      <c r="F40" s="5">
-        <v>23</v>
+      <c r="B40" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C40" s="2">
+        <v>12.01</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E40" s="2">
+        <v>12.11</v>
+      </c>
+      <c r="F40" s="2">
+        <v>21.245000000000001</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="4">
-        <v>2024</v>
-      </c>
-      <c r="C41" s="5">
-        <v>10.039999999999999</v>
-      </c>
-      <c r="D41" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="E41" s="5">
-        <v>10.09</v>
-      </c>
-      <c r="F41" s="5">
-        <v>24.640999999999998</v>
+      <c r="B41" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C41" s="2">
+        <v>11.37</v>
+      </c>
+      <c r="D41" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E41" s="2">
+        <v>11.44</v>
+      </c>
+      <c r="F41" s="2">
+        <v>21.126000000000001</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C42" s="2">
+        <v>11.48</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E42" s="2">
+        <v>11.61</v>
+      </c>
+      <c r="F42" s="2">
+        <v>21.936</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C43" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E43" s="2">
+        <v>11.01</v>
+      </c>
+      <c r="F43" s="2">
+        <v>23</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C44" s="2">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E44" s="2">
+        <v>10.09</v>
+      </c>
+      <c r="F44" s="2">
+        <v>24.640999999999998</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C45" s="2">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E45" s="2">
+        <v>10.09</v>
+      </c>
+      <c r="F45" s="2">
+        <v>24.6</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B46" s="1">
         <v>2015</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C46" s="2">
         <v>19.5</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D46" s="2">
         <v>1</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E46" s="2">
         <v>20.5</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F46" s="2">
         <v>10.4</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="4">
-        <v>2016</v>
-      </c>
-      <c r="C43" s="5">
-        <v>19</v>
-      </c>
-      <c r="D43" s="5">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5">
-        <v>20</v>
-      </c>
-      <c r="F43" s="5">
-        <v>9.9</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="4">
-        <v>2017</v>
-      </c>
-      <c r="C44" s="5">
-        <v>19.7</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5">
-        <v>20.7</v>
-      </c>
-      <c r="F44" s="5">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C45" s="5">
-        <v>19.7</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5">
-        <v>20.7</v>
-      </c>
-      <c r="F45" s="5">
-        <v>9.9</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" s="4">
-        <v>2019</v>
-      </c>
-      <c r="C46" s="5">
-        <v>19.5</v>
-      </c>
-      <c r="D46" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="E46" s="5">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="F46" s="5">
-        <v>9.5</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="4">
-        <v>2020</v>
-      </c>
-      <c r="C47" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D47" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="E47" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="F47" s="5">
+      <c r="B47" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C47" s="2">
+        <v>19</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2">
+        <v>20</v>
+      </c>
+      <c r="F47" s="2">
         <v>9.9</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
+    <row r="48" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="4">
-        <v>2021</v>
-      </c>
-      <c r="C48" s="5">
-        <v>17.7</v>
-      </c>
-      <c r="D48" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="E48" s="5">
-        <v>18.73</v>
-      </c>
-      <c r="F48" s="5">
-        <v>10.4</v>
+      <c r="B48" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C48" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="F48" s="2">
+        <v>9.6999999999999993</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="4">
-        <v>2022</v>
-      </c>
-      <c r="C49" s="5">
-        <v>15</v>
-      </c>
-      <c r="D49" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="E49" s="5">
-        <v>16.059999999999999</v>
-      </c>
-      <c r="F49" s="5">
-        <v>9.6999999999999993</v>
+      <c r="B49" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C49" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="D49" s="2">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="F49" s="2">
+        <v>9.9</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
+    <row r="50" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="4">
-        <v>2023</v>
-      </c>
-      <c r="C50" s="5">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="D50" s="5">
-        <v>1</v>
-      </c>
-      <c r="E50" s="5">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="F50" s="5">
-        <v>9.9</v>
+      <c r="B50" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C50" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E50" s="2">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="F50" s="2">
+        <v>9.5</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+    <row r="51" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B51" s="4">
-        <v>2024</v>
-      </c>
-      <c r="C51" s="5">
+      <c r="B51" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C51" s="2">
         <v>15.5</v>
       </c>
-      <c r="D51" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="E51" s="5">
-        <v>16.43</v>
-      </c>
-      <c r="F51" s="5">
-        <v>11.8</v>
+      <c r="D51" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="E51" s="2">
+        <v>16.2</v>
+      </c>
+      <c r="F51" s="2">
+        <v>9.9</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="52" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C52" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1.03</v>
+      </c>
+      <c r="E52" s="2">
+        <v>18.73</v>
+      </c>
+      <c r="F52" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C53" s="2">
+        <v>15</v>
+      </c>
+      <c r="D53" s="2">
+        <v>1.06</v>
+      </c>
+      <c r="E53" s="2">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="F53" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C54" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D54" s="2">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F54" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C55" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0.93</v>
+      </c>
+      <c r="E55" s="2">
+        <v>16.43</v>
+      </c>
+      <c r="F55" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="6">
+        <v>2025</v>
+      </c>
+      <c r="C56" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1.18</v>
+      </c>
+      <c r="E56" s="7">
+        <v>19.579999999999998</v>
+      </c>
+      <c r="F56" s="7">
+        <v>12</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>